--- a/Industrials.xlsx
+++ b/Industrials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728C7D88-C79F-4742-9DDD-2527090E6E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283EC43D-1DA0-4C7B-88A7-258589A75AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42870" yWindow="2960" windowWidth="21410" windowHeight="15810" activeTab="1" xr2:uid="{B093D665-270D-44A5-96DD-79BA04ADB2EB}"/>
+    <workbookView xWindow="1930" yWindow="1990" windowWidth="30640" windowHeight="16580" xr2:uid="{B093D665-270D-44A5-96DD-79BA04ADB2EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="619">
   <si>
     <t>Name</t>
   </si>
@@ -1907,6 +1908,9 @@
   </si>
   <si>
     <t>HIVE</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -2129,12 +2133,12 @@
         </row>
         <row r="5">
           <cell r="K5">
-            <v>1006756.3981999999</v>
+            <v>1029257.40369977</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>652287</v>
+            <v>652421</v>
           </cell>
         </row>
       </sheetData>
@@ -2145,6 +2149,40 @@
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>578.75099</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>1482.3689999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>38.585000000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2178,7 +2216,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2212,7 +2250,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2246,7 +2284,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2280,7 +2318,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2314,7 +2352,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2364,17 +2402,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>3521</v>
+            <v>3526</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>36996</v>
+            <v>41647</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>7529</v>
+            <v>7702</v>
           </cell>
         </row>
       </sheetData>
@@ -2468,17 +2506,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>610.13520500000004</v>
+            <v>754</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>17000</v>
+            <v>23674</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>52307</v>
+            <v>53618</v>
           </cell>
         </row>
       </sheetData>
@@ -3091,11 +3129,11 @@
       </c>
       <c r="F4" s="3">
         <f>+[1]Main!$K$5-[1]Main!$K$6</f>
-        <v>354469.39819999994</v>
+        <v>376836.40369976999</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" ref="G4:G11" si="0">+E4-F4</f>
-        <v>343354511.80180001</v>
+        <v>343332144.79630023</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>411</v>
@@ -3127,11 +3165,11 @@
       </c>
       <c r="F5" s="3">
         <f>+[1]Main!$K$5-[1]Main!$K$6</f>
-        <v>354469.39819999994</v>
+        <v>376836.40369976999</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>345155890.60180002</v>
+        <v>345133523.59630024</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>411</v>
@@ -3159,22 +3197,22 @@
       </c>
       <c r="E6" s="3">
         <f>+D6*I6</f>
-        <v>911939</v>
+        <v>913234</v>
       </c>
       <c r="F6" s="3">
         <f>+[2]Main!$K$5-[2]Main!$K$6</f>
-        <v>29467</v>
+        <v>33945</v>
       </c>
       <c r="G6" s="3">
         <f>+E6-F6</f>
-        <v>882472</v>
+        <v>879289</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>417</v>
       </c>
       <c r="I6" s="3">
         <f>+[2]Main!$K$3</f>
-        <v>3521</v>
+        <v>3526</v>
       </c>
       <c r="J6" s="16">
         <v>45560</v>
@@ -3303,22 +3341,22 @@
       </c>
       <c r="E10" s="3">
         <f>+D10*I10</f>
-        <v>106712.6473545</v>
+        <v>131874.6</v>
       </c>
       <c r="F10" s="3">
         <f>+[5]Main!$J$5-[5]Main!$J$6</f>
-        <v>-35307</v>
+        <v>-29944</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>142019.64735450002</v>
+        <v>161818.6</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>414</v>
       </c>
       <c r="I10" s="3">
         <f>+[5]Main!$J$3</f>
-        <v>610.13520500000004</v>
+        <v>754</v>
       </c>
       <c r="J10" s="16">
         <v>45527</v>
@@ -6071,7 +6109,29 @@
         <v>435</v>
       </c>
       <c r="D234" s="15">
-        <v>19.79</v>
+        <v>92.48</v>
+      </c>
+      <c r="E234" s="3">
+        <f>+D234*I234</f>
+        <v>53522.891555200003</v>
+      </c>
+      <c r="F234" s="3">
+        <f>[10]Main!$L$5-[10]Main!$L$6</f>
+        <v>1443.7839999999999</v>
+      </c>
+      <c r="G234" s="3">
+        <f>+E234-F234</f>
+        <v>52079.107555200004</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="I234" s="3">
+        <f>[10]Main!$L$3</f>
+        <v>578.75099</v>
+      </c>
+      <c r="J234" s="16">
+        <v>46202</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -6089,7 +6149,7 @@
         <v>2790.0942647199995</v>
       </c>
       <c r="F235" s="3">
-        <f>+[10]Main!$K$5-[10]Main!$K$6</f>
+        <f>+[11]Main!$K$5-[11]Main!$K$6</f>
         <v>91.647000000000006</v>
       </c>
       <c r="G235" s="3">
@@ -6100,7 +6160,7 @@
         <v>439</v>
       </c>
       <c r="I235" s="3">
-        <f>+[10]Main!$K$3</f>
+        <f>+[11]Main!$K$3</f>
         <v>140.34679399999999</v>
       </c>
       <c r="J235" s="16">
@@ -6223,7 +6283,7 @@
       </c>
     </row>
     <row r="3" spans="1:24">
-      <c r="A3" s="25" t="s">
+      <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
@@ -6234,9 +6294,6 @@
       </c>
     </row>
     <row r="4" spans="1:24">
-      <c r="A4" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B4" t="s">
         <v>33</v>
       </c>
@@ -6245,7 +6302,7 @@
       </c>
     </row>
     <row r="5" spans="1:24">
-      <c r="A5" s="25" t="s">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
@@ -6256,7 +6313,7 @@
       </c>
     </row>
     <row r="6" spans="1:24">
-      <c r="A6" s="25" t="s">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
@@ -6267,9 +6324,6 @@
       </c>
     </row>
     <row r="7" spans="1:24">
-      <c r="A7" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B7" t="s">
         <v>446</v>
       </c>
@@ -6278,9 +6332,6 @@
       </c>
     </row>
     <row r="8" spans="1:24">
-      <c r="A8" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B8" t="s">
         <v>99</v>
       </c>
@@ -6289,7 +6340,7 @@
       </c>
     </row>
     <row r="9" spans="1:24">
-      <c r="A9" s="25" t="s">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9" t="s">
@@ -6300,9 +6351,6 @@
       </c>
     </row>
     <row r="10" spans="1:24">
-      <c r="A10" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B10" t="s">
         <v>125</v>
       </c>
@@ -6311,9 +6359,6 @@
       </c>
     </row>
     <row r="11" spans="1:24">
-      <c r="A11" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B11" t="s">
         <v>127</v>
       </c>
@@ -6322,9 +6367,6 @@
       </c>
     </row>
     <row r="12" spans="1:24">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
       <c r="B12" t="s">
         <v>137</v>
       </c>
@@ -6333,9 +6375,6 @@
       </c>
     </row>
     <row r="13" spans="1:24">
-      <c r="A13" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B13" t="s">
         <v>141</v>
       </c>
@@ -6344,9 +6383,6 @@
       </c>
     </row>
     <row r="14" spans="1:24">
-      <c r="A14" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B14" t="s">
         <v>145</v>
       </c>
@@ -6355,9 +6391,6 @@
       </c>
     </row>
     <row r="15" spans="1:24">
-      <c r="A15" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B15" t="s">
         <v>147</v>
       </c>
@@ -6366,9 +6399,6 @@
       </c>
     </row>
     <row r="16" spans="1:24">
-      <c r="A16" s="25" t="s">
-        <v>19</v>
-      </c>
       <c r="B16" t="s">
         <v>151</v>
       </c>
@@ -6376,10 +6406,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="17" spans="2:3">
       <c r="B17" t="s">
         <v>153</v>
       </c>
@@ -6387,10 +6414,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="18" spans="2:3">
       <c r="B18" t="s">
         <v>166</v>
       </c>
@@ -6398,10 +6422,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="19" spans="2:3">
       <c r="B19" t="s">
         <v>178</v>
       </c>
@@ -6409,10 +6430,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="20" spans="2:3">
       <c r="B20" t="s">
         <v>192</v>
       </c>
@@ -6420,10 +6438,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="21" spans="2:3">
       <c r="B21" t="s">
         <v>218</v>
       </c>
@@ -6431,10 +6446,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="22" spans="2:3">
       <c r="B22" t="s">
         <v>462</v>
       </c>
@@ -6442,10 +6454,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="23" spans="2:3">
       <c r="B23" t="s">
         <v>226</v>
       </c>
@@ -6453,10 +6462,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="24" spans="2:3">
       <c r="B24" t="s">
         <v>228</v>
       </c>
@@ -6464,10 +6470,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="25" spans="2:3">
       <c r="B25" t="s">
         <v>234</v>
       </c>
@@ -6475,10 +6478,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="26" spans="2:3">
       <c r="B26" t="s">
         <v>464</v>
       </c>
@@ -6486,10 +6486,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="27" spans="2:3">
       <c r="B27" t="s">
         <v>244</v>
       </c>
@@ -6497,10 +6494,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="28" spans="2:3">
       <c r="B28" t="s">
         <v>248</v>
       </c>
@@ -6508,10 +6502,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="29" spans="2:3">
       <c r="B29" t="s">
         <v>482</v>
       </c>
@@ -6519,10 +6510,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="30" spans="2:3">
       <c r="B30" t="s">
         <v>260</v>
       </c>
@@ -6530,10 +6518,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="31" spans="2:3">
       <c r="B31" t="s">
         <v>484</v>
       </c>
@@ -6541,10 +6526,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="32" spans="2:3">
       <c r="B32" t="s">
         <v>264</v>
       </c>
@@ -6552,10 +6534,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="33" spans="2:10">
       <c r="B33" t="s">
         <v>286</v>
       </c>
@@ -6563,10 +6542,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="34" spans="2:10">
       <c r="B34" s="1" t="s">
         <v>432</v>
       </c>
@@ -6577,10 +6553,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="35" spans="2:10">
       <c r="B35" t="s">
         <v>292</v>
       </c>
@@ -6588,10 +6561,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="36" spans="2:10">
       <c r="B36" t="s">
         <v>294</v>
       </c>
@@ -6599,10 +6569,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="37" spans="2:10">
       <c r="B37" s="1" t="s">
         <v>440</v>
       </c>
@@ -6617,7 +6584,7 @@
         <v>25613.352716399997</v>
       </c>
       <c r="F37" s="17">
-        <f>+[11]Main!$P$5-[11]Main!$P$6</f>
+        <f>+[12]Main!$P$5-[12]Main!$P$6</f>
         <v>-4872.2999999999993</v>
       </c>
       <c r="G37" s="17">
@@ -6625,7 +6592,7 @@
         <v>30485.652716399996</v>
       </c>
       <c r="H37" s="17">
-        <f>+[11]Main!$P$3</f>
+        <f>+[12]Main!$P$3</f>
         <v>133.264062</v>
       </c>
       <c r="I37" s="2" t="s">
@@ -6635,10 +6602,7 @@
         <v>45684</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="38" spans="2:10">
       <c r="B38" t="s">
         <v>326</v>
       </c>
@@ -6646,10 +6610,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="39" spans="2:10">
       <c r="B39" t="s">
         <v>494</v>
       </c>
@@ -6657,10 +6618,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="40" spans="2:10">
       <c r="B40" t="s">
         <v>496</v>
       </c>
@@ -6668,10 +6626,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="41" spans="2:10">
       <c r="B41" t="s">
         <v>470</v>
       </c>
@@ -6679,10 +6634,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="42" spans="2:10">
       <c r="B42" t="s">
         <v>328</v>
       </c>
@@ -6690,10 +6642,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="43" spans="2:10">
       <c r="B43" s="1" t="s">
         <v>420</v>
       </c>
@@ -6708,7 +6657,7 @@
         <v>7703.1368994900013</v>
       </c>
       <c r="F43" s="17">
-        <f>+[12]Main!$N$5-[12]Main!$N$6</f>
+        <f>+[13]Main!$N$5-[13]Main!$N$6</f>
         <v>-22435</v>
       </c>
       <c r="G43" s="17">
@@ -6716,7 +6665,7 @@
         <v>30138.13689949</v>
       </c>
       <c r="H43" s="17">
-        <f>+[12]Main!$N$3</f>
+        <f>+[13]Main!$N$3</f>
         <v>656.70391300000006</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -6726,10 +6675,7 @@
         <v>45561</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="44" spans="2:10">
       <c r="B44" t="s">
         <v>358</v>
       </c>
@@ -6737,7 +6683,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="2:10">
       <c r="B45" s="1" t="s">
         <v>422</v>
       </c>
@@ -6752,7 +6698,7 @@
         <v>7506.67642118</v>
       </c>
       <c r="F45" s="17">
-        <f>+[13]Main!$L$5-[13]Main!$L$6</f>
+        <f>+[14]Main!$L$5-[14]Main!$L$6</f>
         <v>-1587</v>
       </c>
       <c r="G45" s="17">
@@ -6760,7 +6706,7 @@
         <v>9093.67642118</v>
       </c>
       <c r="H45" s="17">
-        <f>+[13]Main!$L$3</f>
+        <f>+[14]Main!$L$3</f>
         <v>80.079757000000001</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -6770,7 +6716,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="2:10">
       <c r="B46" s="1" t="s">
         <v>431</v>
       </c>
@@ -6785,7 +6731,7 @@
         <v>6479.0687500000004</v>
       </c>
       <c r="F46" s="17">
-        <f>+[14]Main!$H$5-[14]Main!$H$6</f>
+        <f>+[15]Main!$H$5-[15]Main!$H$6</f>
         <v>-1307.2</v>
       </c>
       <c r="G46" s="17">
@@ -6793,7 +6739,7 @@
         <v>7786.2687500000002</v>
       </c>
       <c r="H46" s="17">
-        <f>+[14]Main!$H$3</f>
+        <f>+[15]Main!$H$3</f>
         <v>185.11625000000001</v>
       </c>
       <c r="I46" s="2" t="s">
@@ -6803,10 +6749,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="47" spans="2:10">
       <c r="B47" t="s">
         <v>386</v>
       </c>
@@ -6814,10 +6757,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="48" spans="2:10">
       <c r="B48" t="s">
         <v>522</v>
       </c>
@@ -6825,10 +6765,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="49" spans="2:3">
       <c r="B49" t="s">
         <v>547</v>
       </c>
@@ -6836,10 +6773,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="50" spans="2:3">
       <c r="B50" t="s">
         <v>557</v>
       </c>
@@ -6847,10 +6781,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="51" spans="2:3">
       <c r="B51" t="s">
         <v>466</v>
       </c>
@@ -6858,10 +6789,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="52" spans="2:3">
       <c r="B52" t="s">
         <v>539</v>
       </c>
@@ -6869,10 +6797,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="53" spans="2:3">
       <c r="B53" t="s">
         <v>556</v>
       </c>
@@ -6880,10 +6805,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="54" spans="2:3">
       <c r="B54" t="s">
         <v>561</v>
       </c>
@@ -6891,10 +6813,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="55" spans="2:3">
       <c r="B55" t="s">
         <v>553</v>
       </c>
@@ -6902,10 +6821,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="56" spans="2:3">
       <c r="B56" t="s">
         <v>512</v>
       </c>
@@ -6913,10 +6829,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="57" spans="2:3">
       <c r="B57" t="s">
         <v>573</v>
       </c>
@@ -6924,10 +6837,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="58" spans="2:3">
       <c r="B58" t="s">
         <v>577</v>
       </c>
@@ -6935,10 +6845,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="59" spans="2:3">
       <c r="B59" t="s">
         <v>593</v>
       </c>
@@ -6946,10 +6853,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="60" spans="2:3">
       <c r="B60" t="s">
         <v>599</v>
       </c>
@@ -6957,10 +6861,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="61" spans="2:3">
       <c r="B61" t="s">
         <v>601</v>
       </c>
@@ -6968,10 +6869,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="62" spans="2:3">
       <c r="B62" t="s">
         <v>605</v>
       </c>
@@ -6979,10 +6877,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="63" spans="2:3">
       <c r="B63" t="s">
         <v>607</v>
       </c>
@@ -6990,10 +6885,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="25" t="s">
-        <v>19</v>
-      </c>
+    <row r="64" spans="2:3">
       <c r="B64" t="s">
         <v>394</v>
       </c>
@@ -7016,7 +6908,7 @@
         <v>1224.3758563199999</v>
       </c>
       <c r="F65" s="17">
-        <f>+[15]Main!$K$5-[15]Main!$K$6</f>
+        <f>+[16]Main!$K$5-[16]Main!$K$6</f>
         <v>95.133999999999986</v>
       </c>
       <c r="G65" s="17">
@@ -7024,7 +6916,7 @@
         <v>1129.2418563199999</v>
       </c>
       <c r="H65" s="17">
-        <f>+[15]Main!$K$3</f>
+        <f>+[16]Main!$K$3</f>
         <v>206.820246</v>
       </c>
       <c r="I65" s="16" t="s">
